--- a/roster.xlsx
+++ b/roster.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D361"/>
+  <dimension ref="A1:D295"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,5047 +415,4123 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>100001</v>
+        <v>Q763285</v>
       </c>
       <c r="B2" t="str">
-        <v>عنصر رقم 001</v>
+        <v>احمد بدر الدين القرقور</v>
       </c>
       <c r="C2" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D2" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>100002</v>
+        <v>R350649</v>
       </c>
       <c r="B3" t="str">
-        <v>عنصر رقم 002</v>
+        <v>احمد جمال راجح</v>
       </c>
       <c r="C3" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D3" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>100003</v>
+        <v>R628610</v>
       </c>
       <c r="B4" t="str">
-        <v>عنصر رقم 003</v>
+        <v>احمد خالد العباس</v>
       </c>
       <c r="C4" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D4" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>100004</v>
+        <v>R596055</v>
       </c>
       <c r="B5" t="str">
-        <v>عنصر رقم 004</v>
+        <v>احمد خالد ملوك</v>
       </c>
       <c r="C5" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D5" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>100005</v>
+        <v>G945800</v>
       </c>
       <c r="B6" t="str">
-        <v>عنصر رقم 005</v>
+        <v>احمد سليمان الحريري</v>
       </c>
       <c r="C6" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D6" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>100006</v>
+        <v>R675719</v>
       </c>
       <c r="B7" t="str">
-        <v>عنصر رقم 006</v>
+        <v>احمد عدنان جمعة</v>
       </c>
       <c r="C7" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D7" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>100007</v>
+        <v>R618323</v>
       </c>
       <c r="B8" t="str">
-        <v>عنصر رقم 007</v>
+        <v>احمد محمد البحير</v>
       </c>
       <c r="C8" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D8" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>100008</v>
+        <v>R853083</v>
       </c>
       <c r="B9" t="str">
-        <v>عنصر رقم 008</v>
+        <v>ادهم خالد الحسين المصري</v>
       </c>
       <c r="C9" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D9" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>100009</v>
+        <v>R549742</v>
       </c>
       <c r="B10" t="str">
-        <v>عنصر رقم 009</v>
+        <v>اسعد خضر العلي</v>
       </c>
       <c r="C10" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D10" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>100010</v>
+        <v>R367691</v>
       </c>
       <c r="B11" t="str">
-        <v>عنصر رقم 010</v>
+        <v>انس خالد البراقي</v>
       </c>
       <c r="C11" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D11" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>100011</v>
+        <v>R337251</v>
       </c>
       <c r="B12" t="str">
-        <v>عنصر رقم 011</v>
+        <v>إبراهيم محمد البحير</v>
       </c>
       <c r="C12" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D12" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>100012</v>
+        <v>R375371</v>
       </c>
       <c r="B13" t="str">
-        <v>عنصر رقم 012</v>
+        <v>إبراهيم محمد حورية</v>
       </c>
       <c r="C13" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D13" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>100013</v>
+        <v>R874943</v>
       </c>
       <c r="B14" t="str">
-        <v>عنصر رقم 013</v>
+        <v>إسماعيل نايف عودة</v>
       </c>
       <c r="C14" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D14" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>100014</v>
+        <v>R487065</v>
       </c>
       <c r="B15" t="str">
-        <v>عنصر رقم 014</v>
+        <v>أمجد لؤي أحمد</v>
       </c>
       <c r="C15" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D15" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>100015</v>
+        <v>R135034</v>
       </c>
       <c r="B16" t="str">
-        <v>عنصر رقم 015</v>
+        <v>أيوب هاشم زين الدين</v>
       </c>
       <c r="C16" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D16" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>100016</v>
+        <v>R670251</v>
       </c>
       <c r="B17" t="str">
-        <v>عنصر رقم 016</v>
+        <v>باسل محمد هلال</v>
       </c>
       <c r="C17" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D17" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>100017</v>
+        <v>R549164</v>
       </c>
       <c r="B18" t="str">
-        <v>عنصر رقم 017</v>
+        <v>بدر يحيى عديل</v>
       </c>
       <c r="C18" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D18" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>100018</v>
+        <v>R845964</v>
       </c>
       <c r="B19" t="str">
-        <v>عنصر رقم 018</v>
+        <v>بشار حسين البرتاوي</v>
       </c>
       <c r="C19" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D19" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>100019</v>
+        <v>R271115</v>
       </c>
       <c r="B20" t="str">
-        <v>عنصر رقم 019</v>
+        <v>بشار فضل خليل الرفاعي</v>
       </c>
       <c r="C20" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D20" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>100020</v>
+        <v>R271628</v>
       </c>
       <c r="B21" t="str">
-        <v>عنصر رقم 020</v>
+        <v>بهيج طارق عديل</v>
       </c>
       <c r="C21" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D21" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>100021</v>
+        <v>R617791</v>
       </c>
       <c r="B22" t="str">
-        <v>عنصر رقم 021</v>
+        <v>جميل محمد غنيم</v>
       </c>
       <c r="C22" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D22" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>100022</v>
+        <v>R604631</v>
       </c>
       <c r="B23" t="str">
-        <v>عنصر رقم 022</v>
+        <v>حذيفة مسعود قطيمش</v>
       </c>
       <c r="C23" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D23" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>100023</v>
+        <v>G459495</v>
       </c>
       <c r="B24" t="str">
-        <v>عنصر رقم 023</v>
+        <v>حسين اكرم الابراهيم</v>
       </c>
       <c r="C24" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D24" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>100024</v>
+        <v>R270221</v>
       </c>
       <c r="B25" t="str">
-        <v>عنصر رقم 024</v>
+        <v>حمزة محمد جمعة</v>
       </c>
       <c r="C25" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D25" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>100025</v>
+        <v>R904039</v>
       </c>
       <c r="B26" t="str">
-        <v>عنصر رقم 025</v>
+        <v>خلدون احمد خلوف</v>
       </c>
       <c r="C26" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D26" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>100026</v>
+        <v>R937825</v>
       </c>
       <c r="B27" t="str">
-        <v>عنصر رقم 026</v>
+        <v>خليل محمد بريتاوي</v>
       </c>
       <c r="C27" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D27" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>100027</v>
+        <v>R255545</v>
       </c>
       <c r="B28" t="str">
-        <v>عنصر رقم 027</v>
+        <v>رامي خالد الرفاعي</v>
       </c>
       <c r="C28" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D28" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>100028</v>
+        <v>R342332</v>
       </c>
       <c r="B29" t="str">
-        <v>عنصر رقم 028</v>
+        <v>رفيق أحمد المصري</v>
       </c>
       <c r="C29" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D29" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>100029</v>
+        <v>R980916</v>
       </c>
       <c r="B30" t="str">
-        <v>عنصر رقم 029</v>
+        <v>زاهر بشار وهبة</v>
       </c>
       <c r="C30" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D30" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>100030</v>
+        <v>R385638</v>
       </c>
       <c r="B31" t="str">
-        <v>عنصر رقم 030</v>
+        <v>زيد بسام مريج</v>
       </c>
       <c r="C31" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D31" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>100031</v>
+        <v>N869088</v>
       </c>
       <c r="B32" t="str">
-        <v>عنصر رقم 031</v>
+        <v>زيد علي عمر</v>
       </c>
       <c r="C32" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D32" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>100032</v>
+        <v>G895506</v>
       </c>
       <c r="B33" t="str">
-        <v>عنصر رقم 032</v>
+        <v>سالم محمد سعيد</v>
       </c>
       <c r="C33" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D33" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>100033</v>
+        <v>N738100</v>
       </c>
       <c r="B34" t="str">
-        <v>عنصر رقم 033</v>
+        <v>سامر مهدي المحمد</v>
       </c>
       <c r="C34" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D34" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>100034</v>
+        <v>G846858</v>
       </c>
       <c r="B35" t="str">
-        <v>عنصر رقم 034</v>
+        <v>سليمان منير الأحمد</v>
       </c>
       <c r="C35" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D35" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>100035</v>
+        <v>R217010</v>
       </c>
       <c r="B36" t="str">
-        <v>عنصر رقم 035</v>
+        <v>صالح فايز تويم</v>
       </c>
       <c r="C36" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D36" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>100036</v>
+        <v>R434955</v>
       </c>
       <c r="B37" t="str">
-        <v>عنصر رقم 036</v>
+        <v>صبحي علي شيخة</v>
       </c>
       <c r="C37" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D37" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>100037</v>
+        <v>R775572</v>
       </c>
       <c r="B38" t="str">
-        <v>عنصر رقم 037</v>
+        <v>طالب يحيى قلاع</v>
       </c>
       <c r="C38" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D38" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>100038</v>
+        <v>R793393</v>
       </c>
       <c r="B39" t="str">
-        <v>عنصر رقم 038</v>
+        <v>عامر محمد جديع</v>
       </c>
       <c r="C39" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D39" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>100039</v>
+        <v>N133970</v>
       </c>
       <c r="B40" t="str">
-        <v>عنصر رقم 039</v>
+        <v>عبد الاله نايف العيشات</v>
       </c>
       <c r="C40" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D40" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>100040</v>
+        <v>R654877</v>
       </c>
       <c r="B41" t="str">
-        <v>عنصر رقم 040</v>
+        <v>عبد الحليم محمد قسوات</v>
       </c>
       <c r="C41" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D41" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>100041</v>
+        <v>R742904</v>
       </c>
       <c r="B42" t="str">
-        <v>عنصر رقم 041</v>
+        <v>عبد الرحمن خالد العليان</v>
       </c>
       <c r="C42" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D42" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>100042</v>
+        <v>G240618</v>
       </c>
       <c r="B43" t="str">
-        <v>عنصر رقم 042</v>
+        <v>عبد الرحمن علي الجبر</v>
       </c>
       <c r="C43" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D43" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>100043</v>
+        <v>R331852</v>
       </c>
       <c r="B44" t="str">
-        <v>عنصر رقم 043</v>
+        <v>عبد القادر محمد قسوات</v>
       </c>
       <c r="C44" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D44" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>100044</v>
+        <v>R606527</v>
       </c>
       <c r="B45" t="str">
-        <v>عنصر رقم 044</v>
+        <v>عبد الله خالد العمار</v>
       </c>
       <c r="C45" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D45" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>100045</v>
+        <v>N765399</v>
       </c>
       <c r="B46" t="str">
-        <v>عنصر رقم 045</v>
+        <v>عبد الله غازي القرفان</v>
       </c>
       <c r="C46" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D46" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>100046</v>
+        <v>R780495</v>
       </c>
       <c r="B47" t="str">
-        <v>عنصر رقم 046</v>
+        <v>عبد المالك عدنان الهلالي</v>
       </c>
       <c r="C47" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D47" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>100047</v>
+        <v>R721053</v>
       </c>
       <c r="B48" t="str">
-        <v>عنصر رقم 047</v>
+        <v>عبد الهادي حسن غبيس</v>
       </c>
       <c r="C48" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D48" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>100048</v>
+        <v>G350800</v>
       </c>
       <c r="B49" t="str">
-        <v>عنصر رقم 048</v>
+        <v>عبدالرحمن محمد الحريري</v>
       </c>
       <c r="C49" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D49" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>100049</v>
+        <v>R787917</v>
       </c>
       <c r="B50" t="str">
-        <v>عنصر رقم 049</v>
+        <v>عدنان احمد عبد المنعم</v>
       </c>
       <c r="C50" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D50" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>100050</v>
+        <v>R839795</v>
       </c>
       <c r="B51" t="str">
-        <v>عنصر رقم 050</v>
+        <v>عدي موسى العليان</v>
       </c>
       <c r="C51" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D51" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>100051</v>
+        <v>Q967936</v>
       </c>
       <c r="B52" t="str">
-        <v>عنصر رقم 051</v>
+        <v>عفاش ابراهيم الوهبان</v>
       </c>
       <c r="C52" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D52" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>100052</v>
+        <v>R466190</v>
       </c>
       <c r="B53" t="str">
-        <v>عنصر رقم 052</v>
+        <v>علاء موفق ملوك</v>
       </c>
       <c r="C53" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D53" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>100053</v>
+        <v>R229856</v>
       </c>
       <c r="B54" t="str">
-        <v>عنصر رقم 053</v>
+        <v>علاء وليد براقي</v>
       </c>
       <c r="C54" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D54" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>100054</v>
+        <v>G375538</v>
       </c>
       <c r="B55" t="str">
-        <v>عنصر رقم 054</v>
+        <v>علي احمد علي</v>
       </c>
       <c r="C55" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D55" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>100055</v>
+        <v>R702984</v>
       </c>
       <c r="B56" t="str">
-        <v>عنصر رقم 055</v>
+        <v>علي جمعة جمعة</v>
       </c>
       <c r="C56" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D56" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>100056</v>
+        <v>Q474075</v>
       </c>
       <c r="B57" t="str">
-        <v>عنصر رقم 056</v>
+        <v>علي محمد زريق</v>
       </c>
       <c r="C57" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D57" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>100057</v>
+        <v>G520253</v>
       </c>
       <c r="B58" t="str">
-        <v>عنصر رقم 057</v>
+        <v>عمار حسين الخطيب</v>
       </c>
       <c r="C58" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D58" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>100058</v>
+        <v>G209947</v>
       </c>
       <c r="B59" t="str">
-        <v>عنصر رقم 058</v>
+        <v>عمر خالد ابو حصيني</v>
       </c>
       <c r="C59" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D59" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>100059</v>
+        <v>R543785</v>
       </c>
       <c r="B60" t="str">
-        <v>عنصر رقم 059</v>
+        <v>عمر سميح الذياب</v>
       </c>
       <c r="C60" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D60" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>100060</v>
+        <v>R504648</v>
       </c>
       <c r="B61" t="str">
-        <v>عنصر رقم 060</v>
+        <v>عمر معتز الطويل</v>
       </c>
       <c r="C61" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D61" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>100061</v>
+        <v>N253915</v>
       </c>
       <c r="B62" t="str">
-        <v>عنصر رقم 061</v>
+        <v>فوزي محمد الكيلاني</v>
       </c>
       <c r="C62" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D62" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>100062</v>
+        <v>N204856</v>
       </c>
       <c r="B63" t="str">
-        <v>عنصر رقم 062</v>
+        <v>قاسم محمد الأحمد</v>
       </c>
       <c r="C63" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D63" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>100063</v>
+        <v>Q243999</v>
       </c>
       <c r="B64" t="str">
-        <v>عنصر رقم 063</v>
+        <v>لؤي صلاح الغوطاني</v>
       </c>
       <c r="C64" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D64" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>100064</v>
+        <v>R589235</v>
       </c>
       <c r="B65" t="str">
-        <v>عنصر رقم 064</v>
+        <v>مامون دياب برهمجي</v>
       </c>
       <c r="C65" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D65" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>100065</v>
+        <v>R634291</v>
       </c>
       <c r="B66" t="str">
-        <v>عنصر رقم 065</v>
+        <v>مجد محمود الحوراني</v>
       </c>
       <c r="C66" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D66" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>100066</v>
+        <v>MN49343</v>
       </c>
       <c r="B67" t="str">
-        <v>عنصر رقم 066</v>
+        <v>محمد احمد الصيص</v>
       </c>
       <c r="C67" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D67" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>100067</v>
+        <v>R480825</v>
       </c>
       <c r="B68" t="str">
-        <v>عنصر رقم 067</v>
+        <v>محمد احمد عاشور</v>
       </c>
       <c r="C68" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D68" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>100068</v>
+        <v>G159817</v>
       </c>
       <c r="B69" t="str">
-        <v>عنصر رقم 068</v>
+        <v>محمد اقبال عدنان المصري</v>
       </c>
       <c r="C69" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D69" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>100069</v>
+        <v>R995858</v>
       </c>
       <c r="B70" t="str">
-        <v>عنصر رقم 069</v>
+        <v>محمد إبي خالد الحسني</v>
       </c>
       <c r="C70" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D70" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>100070</v>
+        <v>R788702</v>
       </c>
       <c r="B71" t="str">
-        <v>عنصر رقم 070</v>
+        <v>محمد أسامة راجح</v>
       </c>
       <c r="C71" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D71" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>100071</v>
+        <v>R973499</v>
       </c>
       <c r="B72" t="str">
-        <v>عنصر رقم 071</v>
+        <v>محمد أمين خالد شريفة</v>
       </c>
       <c r="C72" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D72" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>100072</v>
+        <v>N180257</v>
       </c>
       <c r="B73" t="str">
-        <v>عنصر رقم 072</v>
+        <v>محمد جهاد الذياب</v>
       </c>
       <c r="C73" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D73" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>100073</v>
+        <v>G268838</v>
       </c>
       <c r="B74" t="str">
-        <v>عنصر رقم 073</v>
+        <v>محمد حسين المصالحة</v>
       </c>
       <c r="C74" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D74" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>100074</v>
+        <v>Q623373</v>
       </c>
       <c r="B75" t="str">
-        <v>عنصر رقم 074</v>
+        <v>محمد حسين صقر</v>
       </c>
       <c r="C75" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D75" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>100075</v>
+        <v>R712814</v>
       </c>
       <c r="B76" t="str">
-        <v>عنصر رقم 075</v>
+        <v>محمد خالد الرفاعي</v>
       </c>
       <c r="C76" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D76" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>100076</v>
+        <v>R678168</v>
       </c>
       <c r="B77" t="str">
-        <v>عنصر رقم 076</v>
+        <v>محمد خليل ملوك</v>
       </c>
       <c r="C77" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D77" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>100077</v>
+        <v>R632728</v>
       </c>
       <c r="B78" t="str">
-        <v>عنصر رقم 077</v>
+        <v>محمد راغد القرصة</v>
       </c>
       <c r="C78" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D78" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>100078</v>
+        <v>R829428</v>
       </c>
       <c r="B79" t="str">
-        <v>عنصر رقم 078</v>
+        <v>محمد سامي الغباغبي</v>
       </c>
       <c r="C79" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D79" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>100079</v>
+        <v>Q713103</v>
       </c>
       <c r="B80" t="str">
-        <v>عنصر رقم 079</v>
+        <v>محمد سامي علي زغبي</v>
       </c>
       <c r="C80" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D80" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>100080</v>
+        <v>R783981</v>
       </c>
       <c r="B81" t="str">
-        <v>عنصر رقم 080</v>
+        <v>محمد صالح عوض</v>
       </c>
       <c r="C81" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D81" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>100081</v>
+        <v>G521913</v>
       </c>
       <c r="B82" t="str">
-        <v>عنصر رقم 081</v>
+        <v>محمد صلاح المقداد</v>
       </c>
       <c r="C82" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D82" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>100082</v>
+        <v>Q844536</v>
       </c>
       <c r="B83" t="str">
-        <v>عنصر رقم 082</v>
+        <v>محمد عبد الرحيم بكر</v>
       </c>
       <c r="C83" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D83" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>100083</v>
+        <v>R696822</v>
       </c>
       <c r="B84" t="str">
-        <v>عنصر رقم 083</v>
+        <v>محمد عبد الكريم شداد</v>
       </c>
       <c r="C84" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D84" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>100084</v>
+        <v>Q155833</v>
       </c>
       <c r="B85" t="str">
-        <v>عنصر رقم 084</v>
+        <v>محمد عبد الناصر الحاج علي</v>
       </c>
       <c r="C85" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D85" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>100085</v>
+        <v>Q162155</v>
       </c>
       <c r="B86" t="str">
-        <v>عنصر رقم 085</v>
+        <v>محمد عبدالله درة</v>
       </c>
       <c r="C86" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D86" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>100086</v>
+        <v>G256008</v>
       </c>
       <c r="B87" t="str">
-        <v>عنصر رقم 086</v>
+        <v>محمد عبدو عصام  ابو حصيني</v>
       </c>
       <c r="C87" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D87" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>100087</v>
+        <v>G215543</v>
       </c>
       <c r="B88" t="str">
-        <v>عنصر رقم 087</v>
+        <v>محمد علي الجبر</v>
       </c>
       <c r="C88" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D88" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>100088</v>
+        <v>R468730</v>
       </c>
       <c r="B89" t="str">
-        <v>عنصر رقم 088</v>
+        <v>محمد عمر راجح</v>
       </c>
       <c r="C89" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D89" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>100089</v>
+        <v>R597328</v>
       </c>
       <c r="B90" t="str">
-        <v>عنصر رقم 089</v>
+        <v>محمد عيد عيسى اعرار</v>
       </c>
       <c r="C90" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D90" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>100090</v>
+        <v>R734734</v>
       </c>
       <c r="B91" t="str">
-        <v>عنصر رقم 090</v>
+        <v>محمد غازي الجبر المفعلاني</v>
       </c>
       <c r="C91" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D91" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>100091</v>
+        <v>N370314</v>
       </c>
       <c r="B92" t="str">
-        <v>عنصر رقم 091</v>
+        <v>محمد غسان أحمد</v>
       </c>
       <c r="C92" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D92" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>100092</v>
+        <v>N173679</v>
       </c>
       <c r="B93" t="str">
-        <v>عنصر رقم 092</v>
+        <v>محمد غسان مطرود</v>
       </c>
       <c r="C93" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D93" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>100093</v>
+        <v>R125063</v>
       </c>
       <c r="B94" t="str">
-        <v>عنصر رقم 093</v>
+        <v>محمد فايز أبو جديد</v>
       </c>
       <c r="C94" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D94" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>100094</v>
+        <v>R676899</v>
       </c>
       <c r="B95" t="str">
-        <v>عنصر رقم 094</v>
+        <v>محمد فراس زين العابدين</v>
       </c>
       <c r="C95" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D95" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>100095</v>
+        <v>Q270304</v>
       </c>
       <c r="B96" t="str">
-        <v>عنصر رقم 095</v>
+        <v>محمد فهد شامية</v>
       </c>
       <c r="C96" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D96" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>100096</v>
+        <v>Q613208</v>
       </c>
       <c r="B97" t="str">
-        <v>عنصر رقم 096</v>
+        <v>محمد فؤاد عبدالعال</v>
       </c>
       <c r="C97" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D97" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>100097</v>
+        <v>G796371</v>
       </c>
       <c r="B98" t="str">
-        <v>عنصر رقم 097</v>
+        <v>محمد فيصل المنصوري</v>
       </c>
       <c r="C98" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D98" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>100098</v>
+        <v>R408382</v>
       </c>
       <c r="B99" t="str">
-        <v>عنصر رقم 098</v>
+        <v>محمد محمود فياض</v>
       </c>
       <c r="C99" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D99" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>100099</v>
+        <v>R736923</v>
       </c>
       <c r="B100" t="str">
-        <v>عنصر رقم 099</v>
+        <v>محمد منير السيد</v>
       </c>
       <c r="C100" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D100" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>100100</v>
+        <v>R617880</v>
       </c>
       <c r="B101" t="str">
-        <v>عنصر رقم 100</v>
+        <v>محمد مهران العاسمي</v>
       </c>
       <c r="C101" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D101" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>100101</v>
+        <v>R384551</v>
       </c>
       <c r="B102" t="str">
-        <v>عنصر رقم 101</v>
+        <v>محمد نضال الصفدي</v>
       </c>
       <c r="C102" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D102" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>100102</v>
+        <v>G498685</v>
       </c>
       <c r="B103" t="str">
-        <v>عنصر رقم 102</v>
+        <v>محمد نضال الكراد</v>
       </c>
       <c r="C103" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D103" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>100103</v>
+        <v>R442825</v>
       </c>
       <c r="B104" t="str">
-        <v>عنصر رقم 103</v>
+        <v>محمد نور خالد العمار</v>
       </c>
       <c r="C104" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D104" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>100104</v>
+        <v>R840644</v>
       </c>
       <c r="B105" t="str">
-        <v>عنصر رقم 104</v>
+        <v>محمد نور عبد العزيز بدران</v>
       </c>
       <c r="C105" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D105" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>100105</v>
+        <v>R488384</v>
       </c>
       <c r="B106" t="str">
-        <v>عنصر رقم 105</v>
+        <v>محمد يوسف المليص</v>
       </c>
       <c r="C106" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D106" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>100106</v>
+        <v>Q125439</v>
       </c>
       <c r="B107" t="str">
-        <v>عنصر رقم 106</v>
+        <v>محمود عيد حيدر</v>
       </c>
       <c r="C107" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D107" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>100107</v>
+        <v>R969524</v>
       </c>
       <c r="B108" t="str">
-        <v>عنصر رقم 107</v>
+        <v>محمود محمد البدوي</v>
       </c>
       <c r="C108" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D108" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>100108</v>
+        <v>R970854</v>
       </c>
       <c r="B109" t="str">
-        <v>عنصر رقم 108</v>
+        <v>مصعب سامي الغباغبي</v>
       </c>
       <c r="C109" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D109" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>100109</v>
+        <v>R552636</v>
       </c>
       <c r="B110" t="str">
-        <v>عنصر رقم 109</v>
+        <v>ملهم محمد السيد</v>
       </c>
       <c r="C110" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D110" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>100110</v>
+        <v>G234430</v>
       </c>
       <c r="B111" t="str">
-        <v>عنصر رقم 110</v>
+        <v>مهدي محمد عليان العوض</v>
       </c>
       <c r="C111" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D111" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>100111</v>
+        <v>Q127428</v>
       </c>
       <c r="B112" t="str">
-        <v>عنصر رقم 111</v>
+        <v>مهند قاسم حسين</v>
       </c>
       <c r="C112" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D112" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>100112</v>
+        <v>Q895572</v>
       </c>
       <c r="B113" t="str">
-        <v>عنصر رقم 112</v>
+        <v>مهند محمد أمين المقداد</v>
       </c>
       <c r="C113" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D113" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>100113</v>
+        <v>R843567</v>
       </c>
       <c r="B114" t="str">
-        <v>عنصر رقم 113</v>
+        <v>مؤمن عمر أبو زيتون</v>
       </c>
       <c r="C114" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D114" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>100114</v>
+        <v>R930303</v>
       </c>
       <c r="B115" t="str">
-        <v>عنصر رقم 114</v>
+        <v>نذير شاكر شاكر</v>
       </c>
       <c r="C115" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D115" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>100115</v>
+        <v>R435078</v>
       </c>
       <c r="B116" t="str">
-        <v>عنصر رقم 115</v>
+        <v>نزار رياض قسوات</v>
       </c>
       <c r="C116" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D116" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>100116</v>
+        <v>Q704754</v>
       </c>
       <c r="B117" t="str">
-        <v>عنصر رقم 116</v>
+        <v>نصر محمد صقر</v>
       </c>
       <c r="C117" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D117" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>100117</v>
+        <v>Q708059</v>
       </c>
       <c r="B118" t="str">
-        <v>عنصر رقم 117</v>
+        <v>هاشم عبد المولى المراد</v>
       </c>
       <c r="C118" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D118" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>100118</v>
+        <v>Q620962</v>
       </c>
       <c r="B119" t="str">
-        <v>عنصر رقم 118</v>
+        <v>وائل احمد الحريري</v>
       </c>
       <c r="C119" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D119" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>100119</v>
+        <v>R217510</v>
       </c>
       <c r="B120" t="str">
-        <v>عنصر رقم 119</v>
+        <v>وائل عبد الغني هلال</v>
       </c>
       <c r="C120" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D120" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>100120</v>
+        <v>G229950</v>
       </c>
       <c r="B121" t="str">
-        <v>عنصر رقم 120</v>
+        <v>وسام قاسم الصبيحي</v>
       </c>
       <c r="C121" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D121" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>100121</v>
+        <v>2408024</v>
       </c>
       <c r="B122" t="str">
-        <v>عنصر رقم 121</v>
+        <v>وسيم علي الزعبي</v>
       </c>
       <c r="C122" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D122" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>100122</v>
+        <v>R162785</v>
       </c>
       <c r="B123" t="str">
-        <v>عنصر رقم 122</v>
+        <v>وليد عدنان الحريري</v>
       </c>
       <c r="C123" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D123" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>100123</v>
+        <v>R557236</v>
       </c>
       <c r="B124" t="str">
-        <v>عنصر رقم 123</v>
+        <v>يحيى احمد الحريري</v>
       </c>
       <c r="C124" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D124" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>100124</v>
+        <v>R817923</v>
       </c>
       <c r="B125" t="str">
-        <v>عنصر رقم 124</v>
+        <v>يحيى ماهر قسوات</v>
       </c>
       <c r="C125" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D125" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>100125</v>
+        <v>R897190</v>
       </c>
       <c r="B126" t="str">
-        <v>عنصر رقم 125</v>
+        <v>يزن خالد بدران</v>
       </c>
       <c r="C126" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D126" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>100126</v>
+        <v>R727134</v>
       </c>
       <c r="B127" t="str">
-        <v>عنصر رقم 126</v>
+        <v>يعقوب احمد شاهين</v>
       </c>
       <c r="C127" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D127" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>100127</v>
+        <v>R388378</v>
       </c>
       <c r="B128" t="str">
-        <v>عنصر رقم 127</v>
+        <v>يمان محمود الجاسم الحريبي</v>
       </c>
       <c r="C128" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D128" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>100128</v>
+        <v>R587196</v>
       </c>
       <c r="B129" t="str">
-        <v>عنصر رقم 128</v>
+        <v>يوسف أسامة الحاج علي</v>
       </c>
       <c r="C129" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D129" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>100129</v>
+        <v>G980819</v>
       </c>
       <c r="B130" t="str">
-        <v>عنصر رقم 129</v>
+        <v>يوسف طه أبو عون</v>
       </c>
       <c r="C130" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D130" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>100130</v>
+        <v>R308316</v>
       </c>
       <c r="B131" t="str">
-        <v>عنصر رقم 130</v>
+        <v>احمد محمد الواوي</v>
       </c>
       <c r="C131" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D131" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>100131</v>
+        <v>R836283</v>
       </c>
       <c r="B132" t="str">
-        <v>عنصر رقم 131</v>
+        <v>أسامة عبد الكريم ملوك</v>
       </c>
       <c r="C132" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D132" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>100132</v>
+        <v>G855473</v>
       </c>
       <c r="B133" t="str">
-        <v>عنصر رقم 132</v>
+        <v>عبدو محمد خطيب</v>
       </c>
       <c r="C133" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D133" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>100133</v>
+        <v>G359240</v>
       </c>
       <c r="B134" t="str">
-        <v>عنصر رقم 133</v>
+        <v>محمد أحمد شلار</v>
       </c>
       <c r="C134" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D134" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>100134</v>
+        <v>R475989</v>
       </c>
       <c r="B135" t="str">
-        <v>عنصر رقم 134</v>
+        <v>محمد حسين إبراهيم</v>
       </c>
       <c r="C135" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D135" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>100135</v>
+        <v>R522107</v>
       </c>
       <c r="B136" t="str">
-        <v>عنصر رقم 135</v>
+        <v>محمد عبد الله براقي</v>
       </c>
       <c r="C136" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D136" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>100136</v>
+        <v>R780327</v>
       </c>
       <c r="B137" t="str">
-        <v>عنصر رقم 136</v>
+        <v>نزار محمد رشواني</v>
       </c>
       <c r="C137" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D137" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>100137</v>
+        <v>R691858</v>
       </c>
       <c r="B138" t="str">
-        <v>عنصر رقم 137</v>
+        <v>يحيى خالد الصغير</v>
       </c>
       <c r="C138" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الأولى</v>
       </c>
       <c r="D138" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>100138</v>
+        <v>R408491</v>
       </c>
       <c r="B139" t="str">
-        <v>عنصر رقم 138</v>
+        <v>امجد احمد الخرمندي</v>
       </c>
       <c r="C139" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D139" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>100139</v>
+        <v>Q307919</v>
       </c>
       <c r="B140" t="str">
-        <v>عنصر رقم 139</v>
+        <v>حسين علي علي</v>
       </c>
       <c r="C140" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D140" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>100140</v>
+        <v>Q179122</v>
       </c>
       <c r="B141" t="str">
-        <v>عنصر رقم 140</v>
+        <v>خالد فظل الشوامره</v>
       </c>
       <c r="C141" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D141" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>100141</v>
+        <v>Q632702</v>
       </c>
       <c r="B142" t="str">
-        <v>عنصر رقم 141</v>
+        <v>عباس عبد الحليم زين العابدين</v>
       </c>
       <c r="C142" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D142" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>100142</v>
+        <v>R415917</v>
       </c>
       <c r="B143" t="str">
-        <v>عنصر رقم 142</v>
+        <v>عبد الاله حسن الملحم</v>
       </c>
       <c r="C143" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D143" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>100143</v>
+        <v>R403010</v>
       </c>
       <c r="B144" t="str">
-        <v>عنصر رقم 143</v>
+        <v>عبد الحكيم عمرجاويش</v>
       </c>
       <c r="C144" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D144" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>100144</v>
+        <v>G155887</v>
       </c>
       <c r="B145" t="str">
-        <v>عنصر رقم 144</v>
+        <v>فهد احمد الحمد النجم</v>
       </c>
       <c r="C145" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D145" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>100145</v>
+        <v>G340483</v>
       </c>
       <c r="B146" t="str">
-        <v>عنصر رقم 145</v>
+        <v>محمد خير عبد الكافي  العلي</v>
       </c>
       <c r="C146" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D146" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>100146</v>
+        <v>R944992</v>
       </c>
       <c r="B147" t="str">
-        <v>عنصر رقم 146</v>
+        <v>محمد سامي الصبيحي</v>
       </c>
       <c r="C147" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D147" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>100147</v>
+        <v>Q623887</v>
       </c>
       <c r="B148" t="str">
-        <v>عنصر رقم 147</v>
+        <v>منذر فريد الرفاعي</v>
       </c>
       <c r="C148" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D148" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>100148</v>
+        <v>G923915</v>
       </c>
       <c r="B149" t="str">
-        <v>عنصر رقم 148</v>
+        <v>ناصر محمود الأحمد</v>
       </c>
       <c r="C149" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D149" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>100149</v>
+        <v>G708230</v>
       </c>
       <c r="B150" t="str">
-        <v>عنصر رقم 149</v>
+        <v>احمد عيسى المسالمة</v>
       </c>
       <c r="C150" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D150" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>100150</v>
+        <v>N344756</v>
       </c>
       <c r="B151" t="str">
-        <v>عنصر رقم 150</v>
+        <v>إبراهيم حسن الغثيان</v>
       </c>
       <c r="C151" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D151" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>100151</v>
+        <v>N174645</v>
       </c>
       <c r="B152" t="str">
-        <v>عنصر رقم 151</v>
+        <v>محمد احمد الشلال</v>
       </c>
       <c r="C152" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D152" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>100152</v>
+        <v>G261533</v>
       </c>
       <c r="B153" t="str">
-        <v>عنصر رقم 152</v>
+        <v>ابراهيم منير النابلسي</v>
       </c>
       <c r="C153" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D153" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>100153</v>
+        <v>R258939</v>
       </c>
       <c r="B154" t="str">
-        <v>عنصر رقم 153</v>
+        <v>اجمل حنيد الحريري</v>
       </c>
       <c r="C154" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D154" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>100154</v>
+        <v>G519503</v>
       </c>
       <c r="B155" t="str">
-        <v>عنصر رقم 154</v>
+        <v>احمد اسامة الرحمون</v>
       </c>
       <c r="C155" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D155" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>100155</v>
+        <v>G218347</v>
       </c>
       <c r="B156" t="str">
-        <v>عنصر رقم 155</v>
+        <v>احمد حبيب ابازيد</v>
       </c>
       <c r="C156" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D156" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>100156</v>
+        <v>R843822</v>
       </c>
       <c r="B157" t="str">
-        <v>عنصر رقم 156</v>
+        <v>احمد دياب راجح</v>
       </c>
       <c r="C157" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D157" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>100157</v>
+        <v>Q902031</v>
       </c>
       <c r="B158" t="str">
-        <v>عنصر رقم 157</v>
+        <v>احمد سعد الدين عرابي</v>
       </c>
       <c r="C158" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D158" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>100158</v>
+        <v>R991304</v>
       </c>
       <c r="B159" t="str">
-        <v>عنصر رقم 158</v>
+        <v>احمد شكري الحوراني</v>
       </c>
       <c r="C159" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D159" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>100159</v>
+        <v>N846692</v>
       </c>
       <c r="B160" t="str">
-        <v>عنصر رقم 159</v>
+        <v>احمد فواز النصرالله</v>
       </c>
       <c r="C160" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D160" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>100160</v>
+        <v>R536668</v>
       </c>
       <c r="B161" t="str">
-        <v>عنصر رقم 160</v>
+        <v>احمد قاسم الكسور</v>
       </c>
       <c r="C161" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D161" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>100161</v>
+        <v>R935410</v>
       </c>
       <c r="B162" t="str">
-        <v>عنصر رقم 161</v>
+        <v>احمد محمد جمعة</v>
       </c>
       <c r="C162" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D162" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>100162</v>
+        <v>R302057</v>
       </c>
       <c r="B163" t="str">
-        <v>عنصر رقم 162</v>
+        <v>احمد محمود حيدر</v>
       </c>
       <c r="C163" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D163" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>100163</v>
+        <v>R697549</v>
       </c>
       <c r="B164" t="str">
-        <v>عنصر رقم 163</v>
+        <v>احمد محمود نوح</v>
       </c>
       <c r="C164" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D164" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>100164</v>
+        <v>R530501</v>
       </c>
       <c r="B165" t="str">
-        <v>عنصر رقم 164</v>
+        <v>ادم اسامه اللباد</v>
       </c>
       <c r="C165" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D165" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>100165</v>
+        <v>R516940</v>
       </c>
       <c r="B166" t="str">
-        <v>عنصر رقم 165</v>
+        <v>اسامه موفق مزعل</v>
       </c>
       <c r="C166" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D166" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>100166</v>
+        <v>G651447</v>
       </c>
       <c r="B167" t="str">
-        <v>عنصر رقم 166</v>
+        <v>انس حسين العلي</v>
       </c>
       <c r="C167" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D167" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>100167</v>
+        <v>R619296</v>
       </c>
       <c r="B168" t="str">
-        <v>عنصر رقم 167</v>
+        <v>ايمن صالح الحشيش</v>
       </c>
       <c r="C168" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D168" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>100168</v>
+        <v>R320099</v>
       </c>
       <c r="B169" t="str">
-        <v>عنصر رقم 168</v>
+        <v>ايمن عيسى الرفاعي</v>
       </c>
       <c r="C169" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D169" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>100169</v>
+        <v>R811427</v>
       </c>
       <c r="B170" t="str">
-        <v>عنصر رقم 169</v>
+        <v>ايهم عبد الرحيم الفروان</v>
       </c>
       <c r="C170" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D170" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>100170</v>
+        <v>G349449</v>
       </c>
       <c r="B171" t="str">
-        <v>عنصر رقم 170</v>
+        <v>إبراهيم ايمن البرماوي</v>
       </c>
       <c r="C171" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D171" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>100171</v>
+        <v>R331948</v>
       </c>
       <c r="B172" t="str">
-        <v>عنصر رقم 171</v>
+        <v>إبراهيم خالد قعبور</v>
       </c>
       <c r="C172" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D172" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>100172</v>
+        <v>G701855</v>
       </c>
       <c r="B173" t="str">
-        <v>عنصر رقم 172</v>
+        <v>إبراهيم خليل جبر</v>
       </c>
       <c r="C173" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D173" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>100173</v>
+        <v>R710978</v>
       </c>
       <c r="B174" t="str">
-        <v>عنصر رقم 173</v>
+        <v>إبراهيم عارف الطايس</v>
       </c>
       <c r="C174" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D174" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>100174</v>
+        <v>G591160</v>
       </c>
       <c r="B175" t="str">
-        <v>عنصر رقم 174</v>
+        <v>إبراهيم علي سلامة</v>
       </c>
       <c r="C175" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D175" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>100175</v>
+        <v>N270519</v>
       </c>
       <c r="B176" t="str">
-        <v>عنصر رقم 175</v>
+        <v>إسماعيل عدنان الدنيفات</v>
       </c>
       <c r="C176" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D176" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>100176</v>
+        <v>R774654</v>
       </c>
       <c r="B177" t="str">
-        <v>عنصر رقم 176</v>
+        <v>أحمد جمال الكردي</v>
       </c>
       <c r="C177" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D177" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>100177</v>
+        <v>R225918</v>
       </c>
       <c r="B178" t="str">
-        <v>عنصر رقم 177</v>
+        <v>أحمد خالد الصاوي</v>
       </c>
       <c r="C178" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D178" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>100178</v>
+        <v>G314364</v>
       </c>
       <c r="B179" t="str">
-        <v>عنصر رقم 178</v>
+        <v>أحمد محمد خير الفرا</v>
       </c>
       <c r="C179" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D179" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>100179</v>
+        <v>R809026</v>
       </c>
       <c r="B180" t="str">
-        <v>عنصر رقم 179</v>
+        <v>أحمد محمد عبد الرحمن</v>
       </c>
       <c r="C180" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D180" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>100180</v>
+        <v>R319959</v>
       </c>
       <c r="B181" t="str">
-        <v>عنصر رقم 180</v>
+        <v>باسل إبراهيم عبد الله</v>
       </c>
       <c r="C181" t="str">
-        <v>كتيبة ١</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D181" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>200001</v>
+        <v>R564152</v>
       </c>
       <c r="B182" t="str">
-        <v>عنصر رقم 001</v>
+        <v>باسل عدنان بريكان</v>
       </c>
       <c r="C182" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D182" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>200002</v>
+        <v>R630864</v>
       </c>
       <c r="B183" t="str">
-        <v>عنصر رقم 002</v>
+        <v>بدر مصباح اليونس</v>
       </c>
       <c r="C183" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D183" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>200003</v>
+        <v>G400635</v>
       </c>
       <c r="B184" t="str">
-        <v>عنصر رقم 003</v>
+        <v>بركات حماد القطاعنة</v>
       </c>
       <c r="C184" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D184" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>200004</v>
+        <v>R224090</v>
       </c>
       <c r="B185" t="str">
-        <v>عنصر رقم 004</v>
+        <v>برهان حيدر الحمد</v>
       </c>
       <c r="C185" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D185" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>200005</v>
+        <v>R448696</v>
       </c>
       <c r="B186" t="str">
-        <v>عنصر رقم 005</v>
+        <v>بشار فؤاد الغزالي</v>
       </c>
       <c r="C186" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D186" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>200006</v>
+        <v>N406697</v>
       </c>
       <c r="B187" t="str">
-        <v>عنصر رقم 006</v>
+        <v>بلال عبد السلام التركماني</v>
       </c>
       <c r="C187" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D187" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>200007</v>
+        <v>R955336</v>
       </c>
       <c r="B188" t="str">
-        <v>عنصر رقم 007</v>
+        <v>بهيج راتب عبد الرحمن</v>
       </c>
       <c r="C188" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D188" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>200008</v>
+        <v>R633159</v>
       </c>
       <c r="B189" t="str">
-        <v>عنصر رقم 008</v>
+        <v>تامر محمد رضوان</v>
       </c>
       <c r="C189" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D189" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>200009</v>
+        <v>R979941</v>
       </c>
       <c r="B190" t="str">
-        <v>عنصر رقم 009</v>
+        <v>جاد الله جهاد فرج</v>
       </c>
       <c r="C190" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D190" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>200010</v>
+        <v>R842895</v>
       </c>
       <c r="B191" t="str">
-        <v>عنصر رقم 010</v>
+        <v>جمال عصام قالوشة</v>
       </c>
       <c r="C191" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D191" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>200011</v>
+        <v>G389513</v>
       </c>
       <c r="B192" t="str">
-        <v>عنصر رقم 011</v>
+        <v>حسام ادريس ادريس</v>
       </c>
       <c r="C192" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D192" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>200012</v>
+        <v>R905360</v>
       </c>
       <c r="B193" t="str">
-        <v>عنصر رقم 012</v>
+        <v>حسن شاكر فرج</v>
       </c>
       <c r="C193" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D193" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>200013</v>
+        <v>N524904</v>
       </c>
       <c r="B194" t="str">
-        <v>عنصر رقم 013</v>
+        <v>حسن محمد المنصور</v>
       </c>
       <c r="C194" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D194" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>200014</v>
+        <v>R763445</v>
       </c>
       <c r="B195" t="str">
-        <v>عنصر رقم 014</v>
+        <v>حسين محمد المطرود</v>
       </c>
       <c r="C195" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D195" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>200015</v>
+        <v>R807569</v>
       </c>
       <c r="B196" t="str">
-        <v>عنصر رقم 015</v>
+        <v>حمزة اسماعيل الحريري</v>
       </c>
       <c r="C196" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D196" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>200016</v>
+        <v>R749738</v>
       </c>
       <c r="B197" t="str">
-        <v>عنصر رقم 016</v>
+        <v>حميد محمود المصري</v>
       </c>
       <c r="C197" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D197" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>200017</v>
+        <v>R354153</v>
       </c>
       <c r="B198" t="str">
-        <v>عنصر رقم 017</v>
+        <v>حيدره  فارس الصعيدي</v>
       </c>
       <c r="C198" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D198" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>200018</v>
+        <v>G368244</v>
       </c>
       <c r="B199" t="str">
-        <v>عنصر رقم 018</v>
+        <v>خالد زاهر السلامه</v>
       </c>
       <c r="C199" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D199" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>200019</v>
+        <v>R283934</v>
       </c>
       <c r="B200" t="str">
-        <v>عنصر رقم 019</v>
+        <v>رامي فايز تويم</v>
       </c>
       <c r="C200" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D200" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>200020</v>
+        <v>R561184</v>
       </c>
       <c r="B201" t="str">
-        <v>عنصر رقم 020</v>
+        <v>رأفت هلال هلال</v>
       </c>
       <c r="C201" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D201" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>200021</v>
+        <v>R664880</v>
       </c>
       <c r="B202" t="str">
-        <v>عنصر رقم 021</v>
+        <v>رعد عبده الطحيمر</v>
       </c>
       <c r="C202" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D202" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>200022</v>
+        <v>N364257</v>
       </c>
       <c r="B203" t="str">
-        <v>عنصر رقم 022</v>
+        <v>رعد عزمي الجدع</v>
       </c>
       <c r="C203" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D203" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>200023</v>
+        <v>N872642</v>
       </c>
       <c r="B204" t="str">
-        <v>عنصر رقم 023</v>
+        <v>رياض حسين نعمه</v>
       </c>
       <c r="C204" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D204" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>200024</v>
+        <v>R789342</v>
       </c>
       <c r="B205" t="str">
-        <v>عنصر رقم 024</v>
+        <v>زيد زياد فرج</v>
       </c>
       <c r="C205" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D205" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>200025</v>
+        <v>G279633</v>
       </c>
       <c r="B206" t="str">
-        <v>عنصر رقم 025</v>
+        <v>سالم زياد سعد الدين</v>
       </c>
       <c r="C206" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D206" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>200026</v>
+        <v>R133544</v>
       </c>
       <c r="B207" t="str">
-        <v>عنصر رقم 026</v>
+        <v>سامي أحمد القعيد</v>
       </c>
       <c r="C207" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D207" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>200027</v>
+        <v>R386129</v>
       </c>
       <c r="B208" t="str">
-        <v>عنصر رقم 027</v>
+        <v>سليمان سليم مزعل</v>
       </c>
       <c r="C208" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D208" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>200028</v>
+        <v>Q655022</v>
       </c>
       <c r="B209" t="str">
-        <v>عنصر رقم 028</v>
+        <v>سليمان ياسر الرمضان</v>
       </c>
       <c r="C209" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D209" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>200029</v>
+        <v>R628094</v>
       </c>
       <c r="B210" t="str">
-        <v>عنصر رقم 029</v>
+        <v>شريف ناصر أبو حمدان</v>
       </c>
       <c r="C210" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D210" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>200030</v>
+        <v>G704862</v>
       </c>
       <c r="B211" t="str">
-        <v>عنصر رقم 030</v>
+        <v>صقر محمد شاهر سعد الدبن</v>
       </c>
       <c r="C211" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D211" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>200031</v>
+        <v>R870910</v>
       </c>
       <c r="B212" t="str">
-        <v>عنصر رقم 031</v>
+        <v>طارق  فرزات حمود</v>
       </c>
       <c r="C212" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D212" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>200032</v>
+        <v>R703130</v>
       </c>
       <c r="B213" t="str">
-        <v>عنصر رقم 032</v>
+        <v>عبد الجليل يوسف مروح</v>
       </c>
       <c r="C213" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D213" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>200033</v>
+        <v>R386992</v>
       </c>
       <c r="B214" t="str">
-        <v>عنصر رقم 033</v>
+        <v>عبد الرحمن احمد سعيد علي</v>
       </c>
       <c r="C214" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D214" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>200034</v>
+        <v>R979767</v>
       </c>
       <c r="B215" t="str">
-        <v>عنصر رقم 034</v>
+        <v>عبد الغني رضوان فتوح</v>
       </c>
       <c r="C215" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D215" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>200035</v>
+        <v>G326935</v>
       </c>
       <c r="B216" t="str">
-        <v>عنصر رقم 035</v>
+        <v>عبد الكريم شاكر المقداد</v>
       </c>
       <c r="C216" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D216" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>200036</v>
+        <v>R543894</v>
       </c>
       <c r="B217" t="str">
-        <v>عنصر رقم 036</v>
+        <v>عبد الله قاسم العليان</v>
       </c>
       <c r="C217" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D217" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>200037</v>
+        <v>N159275</v>
       </c>
       <c r="B218" t="str">
-        <v>عنصر رقم 037</v>
+        <v>عبد الله محمد قسيم</v>
       </c>
       <c r="C218" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D218" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>200038</v>
+        <v>R604550</v>
       </c>
       <c r="B219" t="str">
-        <v>عنصر رقم 038</v>
+        <v>عبدالرحمن احمد المرار الغزالي</v>
       </c>
       <c r="C219" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D219" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>200039</v>
+        <v>G256407</v>
       </c>
       <c r="B220" t="str">
-        <v>عنصر رقم 039</v>
+        <v>عبدالله ياسين الحمدان</v>
       </c>
       <c r="C220" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D220" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>200040</v>
+        <v>R385645</v>
       </c>
       <c r="B221" t="str">
-        <v>عنصر رقم 040</v>
+        <v>عبدالمالك عمار العماري</v>
       </c>
       <c r="C221" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D221" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>200041</v>
+        <v>G329939</v>
       </c>
       <c r="B222" t="str">
-        <v>عنصر رقم 041</v>
+        <v>عبدالمعطي عبداللطيف صالح</v>
       </c>
       <c r="C222" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D222" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>200042</v>
+        <v>R669219</v>
       </c>
       <c r="B223" t="str">
-        <v>عنصر رقم 042</v>
+        <v>عدنان محمد بريتاوي</v>
       </c>
       <c r="C223" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D223" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>200043</v>
+        <v>R780678</v>
       </c>
       <c r="B224" t="str">
-        <v>عنصر رقم 043</v>
+        <v>عرفة نهيل الرفاعي</v>
       </c>
       <c r="C224" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D224" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>200044</v>
+        <v>G346843</v>
       </c>
       <c r="B225" t="str">
-        <v>عنصر رقم 044</v>
+        <v>عزالدين عبد الرزاق الغزاوي</v>
       </c>
       <c r="C225" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D225" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>200045</v>
+        <v>R152457</v>
       </c>
       <c r="B226" t="str">
-        <v>عنصر رقم 045</v>
+        <v>عصام كاظم زين العابدين</v>
       </c>
       <c r="C226" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D226" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>200046</v>
+        <v>R880224</v>
       </c>
       <c r="B227" t="str">
-        <v>عنصر رقم 046</v>
+        <v>علاء كمال المصري</v>
       </c>
       <c r="C227" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D227" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>200047</v>
+        <v>G400153</v>
       </c>
       <c r="B228" t="str">
-        <v>عنصر رقم 047</v>
+        <v>علي حسين الحمد</v>
       </c>
       <c r="C228" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D228" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>200048</v>
+        <v>R713368</v>
       </c>
       <c r="B229" t="str">
-        <v>عنصر رقم 048</v>
+        <v>علي محمد الصائغ</v>
       </c>
       <c r="C229" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D229" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>200049</v>
+        <v>R978266</v>
       </c>
       <c r="B230" t="str">
-        <v>عنصر رقم 049</v>
+        <v>عماد الدين معيوف الأحمد الصالح</v>
       </c>
       <c r="C230" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D230" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>200050</v>
+        <v>R555665</v>
       </c>
       <c r="B231" t="str">
-        <v>عنصر رقم 050</v>
+        <v>عمار ياسر حرفوش</v>
       </c>
       <c r="C231" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D231" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>200051</v>
+        <v>G295952</v>
       </c>
       <c r="B232" t="str">
-        <v>عنصر رقم 051</v>
+        <v>عمر حسن عودة</v>
       </c>
       <c r="C232" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D232" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>200052</v>
+        <v>G785995</v>
       </c>
       <c r="B233" t="str">
-        <v>عنصر رقم 052</v>
+        <v>عمر رضوان عودة</v>
       </c>
       <c r="C233" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D233" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>200053</v>
+        <v>R896720</v>
       </c>
       <c r="B234" t="str">
-        <v>عنصر رقم 053</v>
+        <v>عمر سعيد موسى العليان</v>
       </c>
       <c r="C234" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D234" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>200054</v>
+        <v>G700136</v>
       </c>
       <c r="B235" t="str">
-        <v>عنصر رقم 054</v>
+        <v>عمرو فتحي المقداد</v>
       </c>
       <c r="C235" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D235" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>200055</v>
+        <v>R899641</v>
       </c>
       <c r="B236" t="str">
-        <v>عنصر رقم 055</v>
+        <v>عناد وليد السعد الدين</v>
       </c>
       <c r="C236" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D236" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>200056</v>
+        <v>R504029</v>
       </c>
       <c r="B237" t="str">
-        <v>عنصر رقم 056</v>
+        <v>فاضل محمود حيدر</v>
       </c>
       <c r="C237" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D237" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>200057</v>
+        <v>R377359</v>
       </c>
       <c r="B238" t="str">
-        <v>عنصر رقم 057</v>
+        <v>فراس احمد اللباد</v>
       </c>
       <c r="C238" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D238" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>200058</v>
+        <v>G533895</v>
       </c>
       <c r="B239" t="str">
-        <v>عنصر رقم 058</v>
+        <v>فضاء محمد الجهماني</v>
       </c>
       <c r="C239" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D239" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>200059</v>
+        <v>R947750</v>
       </c>
       <c r="B240" t="str">
-        <v>عنصر رقم 059</v>
+        <v>فهد فراس الحلقي</v>
       </c>
       <c r="C240" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D240" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>200060</v>
+        <v>R579592</v>
       </c>
       <c r="B241" t="str">
-        <v>عنصر رقم 060</v>
+        <v>فهد مصباح الخطيب</v>
       </c>
       <c r="C241" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D241" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>200061</v>
+        <v>G765226</v>
       </c>
       <c r="B242" t="str">
-        <v>عنصر رقم 061</v>
+        <v>فواز محمد شاهر سعد الدين</v>
       </c>
       <c r="C242" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D242" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>200062</v>
+        <v>R670613</v>
       </c>
       <c r="B243" t="str">
-        <v>عنصر رقم 062</v>
+        <v>قاسم محمود الخرمندي</v>
       </c>
       <c r="C243" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D243" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>200063</v>
+        <v>G854839</v>
       </c>
       <c r="B244" t="str">
-        <v>عنصر رقم 063</v>
+        <v>مالك خالد موسى</v>
       </c>
       <c r="C244" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D244" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>200064</v>
+        <v>R490796</v>
       </c>
       <c r="B245" t="str">
-        <v>عنصر رقم 064</v>
+        <v>مجد موسى العليان</v>
       </c>
       <c r="C245" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D245" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>200065</v>
+        <v>N141439</v>
       </c>
       <c r="B246" t="str">
-        <v>عنصر رقم 065</v>
+        <v>محمد احمد الزريقات</v>
       </c>
       <c r="C246" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D246" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>200066</v>
+        <v>R951159</v>
       </c>
       <c r="B247" t="str">
-        <v>عنصر رقم 066</v>
+        <v>محمد احمد العماري</v>
       </c>
       <c r="C247" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D247" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>200067</v>
+        <v>G954680</v>
       </c>
       <c r="B248" t="str">
-        <v>عنصر رقم 067</v>
+        <v>محمد إبراهيم محمود</v>
       </c>
       <c r="C248" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D248" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>200068</v>
+        <v>R565296</v>
       </c>
       <c r="B249" t="str">
-        <v>عنصر رقم 068</v>
+        <v>محمد بسام علي</v>
       </c>
       <c r="C249" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D249" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>200069</v>
+        <v>R479426</v>
       </c>
       <c r="B250" t="str">
-        <v>عنصر رقم 069</v>
+        <v>محمد جهاد الناصر</v>
       </c>
       <c r="C250" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D250" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>200070</v>
+        <v>R586769</v>
       </c>
       <c r="B251" t="str">
-        <v>عنصر رقم 070</v>
+        <v>محمد جهاد جمعة</v>
       </c>
       <c r="C251" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D251" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>200071</v>
+        <v>R376963</v>
       </c>
       <c r="B252" t="str">
-        <v>عنصر رقم 071</v>
+        <v>محمد حسن الصياح</v>
       </c>
       <c r="C252" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D252" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>200072</v>
+        <v>R606799</v>
       </c>
       <c r="B253" t="str">
-        <v>عنصر رقم 072</v>
+        <v>محمد حمود حسن</v>
       </c>
       <c r="C253" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D253" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>200073</v>
+        <v>R837662</v>
       </c>
       <c r="B254" t="str">
-        <v>عنصر رقم 073</v>
+        <v>محمد خير محمود قعبور</v>
       </c>
       <c r="C254" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D254" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>200074</v>
+        <v>R955407</v>
       </c>
       <c r="B255" t="str">
-        <v>عنصر رقم 074</v>
+        <v>محمد ديب عمر الحمدوني</v>
       </c>
       <c r="C255" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D255" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>200075</v>
+        <v>R497105</v>
       </c>
       <c r="B256" t="str">
-        <v>عنصر رقم 075</v>
+        <v>محمد زياد عبدالعال</v>
       </c>
       <c r="C256" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D256" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>200076</v>
+        <v>R571561</v>
       </c>
       <c r="B257" t="str">
-        <v>عنصر رقم 076</v>
+        <v>محمد شاكر فرج</v>
       </c>
       <c r="C257" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D257" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>200077</v>
+        <v>R678984</v>
       </c>
       <c r="B258" t="str">
-        <v>عنصر رقم 077</v>
+        <v>محمد طه لطيفة</v>
       </c>
       <c r="C258" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D258" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>200078</v>
+        <v>R728802</v>
       </c>
       <c r="B259" t="str">
-        <v>عنصر رقم 078</v>
+        <v>محمد عبد الرزاق حمدان</v>
       </c>
       <c r="C259" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D259" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>200079</v>
+        <v>R470221</v>
       </c>
       <c r="B260" t="str">
-        <v>عنصر رقم 079</v>
+        <v>محمد عبد الناصر الريابي</v>
       </c>
       <c r="C260" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D260" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>200080</v>
+        <v>G548126</v>
       </c>
       <c r="B261" t="str">
-        <v>عنصر رقم 080</v>
+        <v>محمد علي المصري</v>
       </c>
       <c r="C261" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D261" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>200081</v>
+        <v>N636583</v>
       </c>
       <c r="B262" t="str">
-        <v>عنصر رقم 081</v>
+        <v>محمد غازي الهيله</v>
       </c>
       <c r="C262" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D262" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>200082</v>
+        <v>R429739</v>
       </c>
       <c r="B263" t="str">
-        <v>عنصر رقم 082</v>
+        <v>محمد فايز الخطيب</v>
       </c>
       <c r="C263" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D263" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>200083</v>
+        <v>R313387</v>
       </c>
       <c r="B264" t="str">
-        <v>عنصر رقم 083</v>
+        <v>محمد محمود الحميدات</v>
       </c>
       <c r="C264" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D264" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>200084</v>
+        <v>R206780</v>
       </c>
       <c r="B265" t="str">
-        <v>عنصر رقم 084</v>
+        <v>محمد محمود الكسور</v>
       </c>
       <c r="C265" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D265" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>200085</v>
+        <v>R113839</v>
       </c>
       <c r="B266" t="str">
-        <v>عنصر رقم 085</v>
+        <v>محمد محمود صعب</v>
       </c>
       <c r="C266" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D266" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>200086</v>
+        <v>R500861</v>
       </c>
       <c r="B267" t="str">
-        <v>عنصر رقم 086</v>
+        <v>محمد نزير الخطيب</v>
       </c>
       <c r="C267" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D267" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>200087</v>
+        <v>R897969</v>
       </c>
       <c r="B268" t="str">
-        <v>عنصر رقم 087</v>
+        <v>محمد نهار البكريه</v>
       </c>
       <c r="C268" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D268" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>200088</v>
+        <v>R783348</v>
       </c>
       <c r="B269" t="str">
-        <v>عنصر رقم 088</v>
+        <v>محمد نور الدين اللباد</v>
       </c>
       <c r="C269" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D269" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>200089</v>
+        <v>R951179</v>
       </c>
       <c r="B270" t="str">
-        <v>عنصر رقم 089</v>
+        <v>محمود حسين صالح</v>
       </c>
       <c r="C270" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D270" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>200090</v>
+        <v>Q111293</v>
       </c>
       <c r="B271" t="str">
-        <v>عنصر رقم 090</v>
+        <v>محمود محمد الحوراني</v>
       </c>
       <c r="C271" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D271" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>200091</v>
+        <v>R698017</v>
       </c>
       <c r="B272" t="str">
-        <v>عنصر رقم 091</v>
+        <v>محمود ناصر عقاب</v>
       </c>
       <c r="C272" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D272" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>200092</v>
+        <v>G471021</v>
       </c>
       <c r="B273" t="str">
-        <v>عنصر رقم 092</v>
+        <v>مرهف نايل الكراد</v>
       </c>
       <c r="C273" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D273" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>200093</v>
+        <v>Q210584</v>
       </c>
       <c r="B274" t="str">
-        <v>عنصر رقم 093</v>
+        <v>مروان هيثم العلي</v>
       </c>
       <c r="C274" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D274" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>200094</v>
+        <v>G699370</v>
       </c>
       <c r="B275" t="str">
-        <v>عنصر رقم 094</v>
+        <v>مصطفى ايمن الخطيب</v>
       </c>
       <c r="C275" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D275" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>200095</v>
+        <v>R803897</v>
       </c>
       <c r="B276" t="str">
-        <v>عنصر رقم 095</v>
+        <v>مصعب فارس العليان</v>
       </c>
       <c r="C276" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D276" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>200096</v>
+        <v>Q325195</v>
       </c>
       <c r="B277" t="str">
-        <v>عنصر رقم 096</v>
+        <v>معاذ عماد جباوي</v>
       </c>
       <c r="C277" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D277" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>200097</v>
+        <v>N309226</v>
       </c>
       <c r="B278" t="str">
-        <v>عنصر رقم 097</v>
+        <v>معتز حمزة قلاع</v>
       </c>
       <c r="C278" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D278" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>200098</v>
+        <v>R115596</v>
       </c>
       <c r="B279" t="str">
-        <v>عنصر رقم 098</v>
+        <v>منصور احمد البدوي</v>
       </c>
       <c r="C279" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D279" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>200099</v>
+        <v>R115296</v>
       </c>
       <c r="B280" t="str">
-        <v>عنصر رقم 099</v>
+        <v>مهند علي الشايب</v>
       </c>
       <c r="C280" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D280" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>200100</v>
+        <v>R946456</v>
       </c>
       <c r="B281" t="str">
-        <v>عنصر رقم 100</v>
+        <v>مهند عمار برهوم</v>
       </c>
       <c r="C281" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D281" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>200101</v>
+        <v>R172032</v>
       </c>
       <c r="B282" t="str">
-        <v>عنصر رقم 101</v>
+        <v>مؤيد عاطف مسلماني</v>
       </c>
       <c r="C282" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D282" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>200102</v>
+        <v>R969518</v>
       </c>
       <c r="B283" t="str">
-        <v>عنصر رقم 102</v>
+        <v>نزار سلطي العليان</v>
       </c>
       <c r="C283" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D283" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>200103</v>
+        <v>G120368</v>
       </c>
       <c r="B284" t="str">
-        <v>عنصر رقم 103</v>
+        <v>نزار ظافر أبو نبوت</v>
       </c>
       <c r="C284" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D284" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>200104</v>
+        <v>R941868</v>
       </c>
       <c r="B285" t="str">
-        <v>عنصر رقم 104</v>
+        <v>وسيم وليد اسعد</v>
       </c>
       <c r="C285" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D285" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>200105</v>
+        <v>Q315829</v>
       </c>
       <c r="B286" t="str">
-        <v>عنصر رقم 105</v>
+        <v>وضاح ثاني العبدالله</v>
       </c>
       <c r="C286" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D286" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>200106</v>
+        <v>R956761</v>
       </c>
       <c r="B287" t="str">
-        <v>عنصر رقم 106</v>
+        <v>يامن عماد الذياب</v>
       </c>
       <c r="C287" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D287" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>200107</v>
+        <v>Q876902</v>
       </c>
       <c r="B288" t="str">
-        <v>عنصر رقم 107</v>
+        <v>يحيى رضوان المحسن</v>
       </c>
       <c r="C288" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D288" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>200108</v>
+        <v>R871926</v>
       </c>
       <c r="B289" t="str">
-        <v>عنصر رقم 108</v>
+        <v>يحيى محمد القدرو</v>
       </c>
       <c r="C289" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D289" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>200109</v>
+        <v>R326603</v>
       </c>
       <c r="B290" t="str">
-        <v>عنصر رقم 109</v>
+        <v>يزن عمر عليوي</v>
       </c>
       <c r="C290" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D290" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>200110</v>
+        <v>G686387</v>
       </c>
       <c r="B291" t="str">
-        <v>عنصر رقم 110</v>
+        <v>يزن محمد شاهر سعد الدين</v>
       </c>
       <c r="C291" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D291" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>200111</v>
+        <v>N341104</v>
       </c>
       <c r="B292" t="str">
-        <v>عنصر رقم 111</v>
+        <v>يزن ناصر السليمان</v>
       </c>
       <c r="C292" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D292" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>200112</v>
+        <v>R921434</v>
       </c>
       <c r="B293" t="str">
-        <v>عنصر رقم 112</v>
+        <v>يوسف أحمد شريدة</v>
       </c>
       <c r="C293" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D293" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>200113</v>
+        <v>Q278350</v>
       </c>
       <c r="B294" t="str">
-        <v>عنصر رقم 113</v>
+        <v>يوسف عدنان ابو عون</v>
       </c>
       <c r="C294" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D294" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>200114</v>
+        <v>N876578</v>
       </c>
       <c r="B295" t="str">
-        <v>عنصر رقم 114</v>
+        <v>بدر محمود الفايز</v>
       </c>
       <c r="C295" t="str">
-        <v>كتيبة ٢</v>
+        <v>الكتيبة الثانية</v>
       </c>
       <c r="D295" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="str">
-        <v>200115</v>
-      </c>
-      <c r="B296" t="str">
-        <v>عنصر رقم 115</v>
-      </c>
-      <c r="C296" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D296" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="str">
-        <v>200116</v>
-      </c>
-      <c r="B297" t="str">
-        <v>عنصر رقم 116</v>
-      </c>
-      <c r="C297" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D297" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="str">
-        <v>200117</v>
-      </c>
-      <c r="B298" t="str">
-        <v>عنصر رقم 117</v>
-      </c>
-      <c r="C298" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D298" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="str">
-        <v>200118</v>
-      </c>
-      <c r="B299" t="str">
-        <v>عنصر رقم 118</v>
-      </c>
-      <c r="C299" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D299" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="str">
-        <v>200119</v>
-      </c>
-      <c r="B300" t="str">
-        <v>عنصر رقم 119</v>
-      </c>
-      <c r="C300" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D300" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="str">
-        <v>200120</v>
-      </c>
-      <c r="B301" t="str">
-        <v>عنصر رقم 120</v>
-      </c>
-      <c r="C301" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D301" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="str">
-        <v>200121</v>
-      </c>
-      <c r="B302" t="str">
-        <v>عنصر رقم 121</v>
-      </c>
-      <c r="C302" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D302" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="str">
-        <v>200122</v>
-      </c>
-      <c r="B303" t="str">
-        <v>عنصر رقم 122</v>
-      </c>
-      <c r="C303" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D303" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="str">
-        <v>200123</v>
-      </c>
-      <c r="B304" t="str">
-        <v>عنصر رقم 123</v>
-      </c>
-      <c r="C304" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D304" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="str">
-        <v>200124</v>
-      </c>
-      <c r="B305" t="str">
-        <v>عنصر رقم 124</v>
-      </c>
-      <c r="C305" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D305" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="str">
-        <v>200125</v>
-      </c>
-      <c r="B306" t="str">
-        <v>عنصر رقم 125</v>
-      </c>
-      <c r="C306" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D306" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="str">
-        <v>200126</v>
-      </c>
-      <c r="B307" t="str">
-        <v>عنصر رقم 126</v>
-      </c>
-      <c r="C307" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D307" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="str">
-        <v>200127</v>
-      </c>
-      <c r="B308" t="str">
-        <v>عنصر رقم 127</v>
-      </c>
-      <c r="C308" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D308" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="str">
-        <v>200128</v>
-      </c>
-      <c r="B309" t="str">
-        <v>عنصر رقم 128</v>
-      </c>
-      <c r="C309" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D309" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="str">
-        <v>200129</v>
-      </c>
-      <c r="B310" t="str">
-        <v>عنصر رقم 129</v>
-      </c>
-      <c r="C310" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D310" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="str">
-        <v>200130</v>
-      </c>
-      <c r="B311" t="str">
-        <v>عنصر رقم 130</v>
-      </c>
-      <c r="C311" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D311" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="str">
-        <v>200131</v>
-      </c>
-      <c r="B312" t="str">
-        <v>عنصر رقم 131</v>
-      </c>
-      <c r="C312" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D312" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="str">
-        <v>200132</v>
-      </c>
-      <c r="B313" t="str">
-        <v>عنصر رقم 132</v>
-      </c>
-      <c r="C313" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D313" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="str">
-        <v>200133</v>
-      </c>
-      <c r="B314" t="str">
-        <v>عنصر رقم 133</v>
-      </c>
-      <c r="C314" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D314" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="str">
-        <v>200134</v>
-      </c>
-      <c r="B315" t="str">
-        <v>عنصر رقم 134</v>
-      </c>
-      <c r="C315" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D315" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="str">
-        <v>200135</v>
-      </c>
-      <c r="B316" t="str">
-        <v>عنصر رقم 135</v>
-      </c>
-      <c r="C316" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D316" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="str">
-        <v>200136</v>
-      </c>
-      <c r="B317" t="str">
-        <v>عنصر رقم 136</v>
-      </c>
-      <c r="C317" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D317" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="str">
-        <v>200137</v>
-      </c>
-      <c r="B318" t="str">
-        <v>عنصر رقم 137</v>
-      </c>
-      <c r="C318" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D318" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="str">
-        <v>200138</v>
-      </c>
-      <c r="B319" t="str">
-        <v>عنصر رقم 138</v>
-      </c>
-      <c r="C319" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D319" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="str">
-        <v>200139</v>
-      </c>
-      <c r="B320" t="str">
-        <v>عنصر رقم 139</v>
-      </c>
-      <c r="C320" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D320" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="str">
-        <v>200140</v>
-      </c>
-      <c r="B321" t="str">
-        <v>عنصر رقم 140</v>
-      </c>
-      <c r="C321" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D321" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="str">
-        <v>200141</v>
-      </c>
-      <c r="B322" t="str">
-        <v>عنصر رقم 141</v>
-      </c>
-      <c r="C322" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D322" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="str">
-        <v>200142</v>
-      </c>
-      <c r="B323" t="str">
-        <v>عنصر رقم 142</v>
-      </c>
-      <c r="C323" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D323" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="str">
-        <v>200143</v>
-      </c>
-      <c r="B324" t="str">
-        <v>عنصر رقم 143</v>
-      </c>
-      <c r="C324" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D324" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="str">
-        <v>200144</v>
-      </c>
-      <c r="B325" t="str">
-        <v>عنصر رقم 144</v>
-      </c>
-      <c r="C325" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D325" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="str">
-        <v>200145</v>
-      </c>
-      <c r="B326" t="str">
-        <v>عنصر رقم 145</v>
-      </c>
-      <c r="C326" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D326" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="str">
-        <v>200146</v>
-      </c>
-      <c r="B327" t="str">
-        <v>عنصر رقم 146</v>
-      </c>
-      <c r="C327" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D327" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="str">
-        <v>200147</v>
-      </c>
-      <c r="B328" t="str">
-        <v>عنصر رقم 147</v>
-      </c>
-      <c r="C328" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D328" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="str">
-        <v>200148</v>
-      </c>
-      <c r="B329" t="str">
-        <v>عنصر رقم 148</v>
-      </c>
-      <c r="C329" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D329" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="str">
-        <v>200149</v>
-      </c>
-      <c r="B330" t="str">
-        <v>عنصر رقم 149</v>
-      </c>
-      <c r="C330" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D330" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="str">
-        <v>200150</v>
-      </c>
-      <c r="B331" t="str">
-        <v>عنصر رقم 150</v>
-      </c>
-      <c r="C331" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D331" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="str">
-        <v>200151</v>
-      </c>
-      <c r="B332" t="str">
-        <v>عنصر رقم 151</v>
-      </c>
-      <c r="C332" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D332" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="str">
-        <v>200152</v>
-      </c>
-      <c r="B333" t="str">
-        <v>عنصر رقم 152</v>
-      </c>
-      <c r="C333" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D333" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="str">
-        <v>200153</v>
-      </c>
-      <c r="B334" t="str">
-        <v>عنصر رقم 153</v>
-      </c>
-      <c r="C334" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D334" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="str">
-        <v>200154</v>
-      </c>
-      <c r="B335" t="str">
-        <v>عنصر رقم 154</v>
-      </c>
-      <c r="C335" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D335" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="str">
-        <v>200155</v>
-      </c>
-      <c r="B336" t="str">
-        <v>عنصر رقم 155</v>
-      </c>
-      <c r="C336" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D336" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="str">
-        <v>200156</v>
-      </c>
-      <c r="B337" t="str">
-        <v>عنصر رقم 156</v>
-      </c>
-      <c r="C337" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D337" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="str">
-        <v>200157</v>
-      </c>
-      <c r="B338" t="str">
-        <v>عنصر رقم 157</v>
-      </c>
-      <c r="C338" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D338" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="str">
-        <v>200158</v>
-      </c>
-      <c r="B339" t="str">
-        <v>عنصر رقم 158</v>
-      </c>
-      <c r="C339" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D339" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="str">
-        <v>200159</v>
-      </c>
-      <c r="B340" t="str">
-        <v>عنصر رقم 159</v>
-      </c>
-      <c r="C340" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D340" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="str">
-        <v>200160</v>
-      </c>
-      <c r="B341" t="str">
-        <v>عنصر رقم 160</v>
-      </c>
-      <c r="C341" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D341" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="str">
-        <v>200161</v>
-      </c>
-      <c r="B342" t="str">
-        <v>عنصر رقم 161</v>
-      </c>
-      <c r="C342" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D342" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="str">
-        <v>200162</v>
-      </c>
-      <c r="B343" t="str">
-        <v>عنصر رقم 162</v>
-      </c>
-      <c r="C343" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D343" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="str">
-        <v>200163</v>
-      </c>
-      <c r="B344" t="str">
-        <v>عنصر رقم 163</v>
-      </c>
-      <c r="C344" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D344" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="str">
-        <v>200164</v>
-      </c>
-      <c r="B345" t="str">
-        <v>عنصر رقم 164</v>
-      </c>
-      <c r="C345" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D345" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="str">
-        <v>200165</v>
-      </c>
-      <c r="B346" t="str">
-        <v>عنصر رقم 165</v>
-      </c>
-      <c r="C346" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D346" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="str">
-        <v>200166</v>
-      </c>
-      <c r="B347" t="str">
-        <v>عنصر رقم 166</v>
-      </c>
-      <c r="C347" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D347" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="str">
-        <v>200167</v>
-      </c>
-      <c r="B348" t="str">
-        <v>عنصر رقم 167</v>
-      </c>
-      <c r="C348" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D348" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="str">
-        <v>200168</v>
-      </c>
-      <c r="B349" t="str">
-        <v>عنصر رقم 168</v>
-      </c>
-      <c r="C349" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D349" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="str">
-        <v>200169</v>
-      </c>
-      <c r="B350" t="str">
-        <v>عنصر رقم 169</v>
-      </c>
-      <c r="C350" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D350" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="str">
-        <v>200170</v>
-      </c>
-      <c r="B351" t="str">
-        <v>عنصر رقم 170</v>
-      </c>
-      <c r="C351" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D351" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="str">
-        <v>200171</v>
-      </c>
-      <c r="B352" t="str">
-        <v>عنصر رقم 171</v>
-      </c>
-      <c r="C352" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D352" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="str">
-        <v>200172</v>
-      </c>
-      <c r="B353" t="str">
-        <v>عنصر رقم 172</v>
-      </c>
-      <c r="C353" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D353" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="str">
-        <v>200173</v>
-      </c>
-      <c r="B354" t="str">
-        <v>عنصر رقم 173</v>
-      </c>
-      <c r="C354" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D354" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="str">
-        <v>200174</v>
-      </c>
-      <c r="B355" t="str">
-        <v>عنصر رقم 174</v>
-      </c>
-      <c r="C355" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D355" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="str">
-        <v>200175</v>
-      </c>
-      <c r="B356" t="str">
-        <v>عنصر رقم 175</v>
-      </c>
-      <c r="C356" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D356" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="str">
-        <v>200176</v>
-      </c>
-      <c r="B357" t="str">
-        <v>عنصر رقم 176</v>
-      </c>
-      <c r="C357" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D357" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="str">
-        <v>200177</v>
-      </c>
-      <c r="B358" t="str">
-        <v>عنصر رقم 177</v>
-      </c>
-      <c r="C358" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D358" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="str">
-        <v>200178</v>
-      </c>
-      <c r="B359" t="str">
-        <v>عنصر رقم 178</v>
-      </c>
-      <c r="C359" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D359" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="str">
-        <v>200179</v>
-      </c>
-      <c r="B360" t="str">
-        <v>عنصر رقم 179</v>
-      </c>
-      <c r="C360" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D360" t="str">
-        <v>النقطة العامة</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="str">
-        <v>200180</v>
-      </c>
-      <c r="B361" t="str">
-        <v>عنصر رقم 180</v>
-      </c>
-      <c r="C361" t="str">
-        <v>كتيبة ٢</v>
-      </c>
-      <c r="D361" t="str">
-        <v>النقطة العامة</v>
+        <v>الفوج الثالث</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D361"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D295"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BASEL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BASEL\Desktop\نظام تفقد\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFDB97B-6827-434A-9964-204F4AB162E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217EE8C9-1373-498F-9EB2-8ADDC2F07667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E3E8A68-987D-4C06-BFB9-2CF7CF2E1A8C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="885">
   <si>
     <t>الجهة الفرعية</t>
   </si>
@@ -2691,6 +2691,9 @@
   </si>
   <si>
     <t>الطيرة</t>
+  </si>
+  <si>
+    <t>الدور</t>
   </si>
 </sst>
 </file>
@@ -2862,15 +2865,7 @@
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="37">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -9830,7 +9825,7 @@
         <v>601</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G261" s="16" t="s">
         <v>657</v>
@@ -9854,7 +9849,7 @@
         <v>601</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G262" s="16" t="s">
         <v>647</v>
@@ -9878,7 +9873,7 @@
         <v>601</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G263" s="16" t="s">
         <v>611</v>
@@ -9902,7 +9897,7 @@
         <v>601</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G264" s="16" t="s">
         <v>732</v>
@@ -9926,7 +9921,7 @@
         <v>601</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G265" s="16" t="s">
         <v>621</v>
@@ -9950,7 +9945,7 @@
         <v>601</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G266" s="16" t="s">
         <v>856</v>
@@ -9974,7 +9969,7 @@
         <v>601</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G267" s="16" t="s">
         <v>749</v>
@@ -9998,7 +9993,7 @@
         <v>601</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G268" s="16" t="s">
         <v>792</v>
@@ -10022,7 +10017,7 @@
         <v>601</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G269" s="16" t="s">
         <v>784</v>
@@ -10046,7 +10041,7 @@
         <v>601</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G270" s="16" t="s">
         <v>842</v>
@@ -10070,7 +10065,7 @@
         <v>601</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G271" s="12"/>
       <c r="J271" s="6"/>
@@ -10092,7 +10087,7 @@
         <v>601</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G272" s="16" t="s">
         <v>660</v>
@@ -10116,7 +10111,7 @@
         <v>601</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G273" s="16" t="s">
         <v>733</v>
@@ -10140,7 +10135,7 @@
         <v>601</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G274" s="16" t="s">
         <v>747</v>
@@ -10164,7 +10159,7 @@
         <v>601</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G275" s="16" t="s">
         <v>880</v>
@@ -10188,7 +10183,7 @@
         <v>601</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G276" s="16" t="s">
         <v>725</v>
@@ -10212,7 +10207,7 @@
         <v>601</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G277" s="16" t="s">
         <v>765</v>
@@ -10236,7 +10231,7 @@
         <v>601</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G278" s="16" t="s">
         <v>730</v>
@@ -10260,7 +10255,7 @@
         <v>601</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G279" s="16" t="s">
         <v>877</v>
@@ -10284,7 +10279,7 @@
         <v>601</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G280" s="16" t="s">
         <v>752</v>
@@ -10308,7 +10303,7 @@
         <v>601</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G281" s="16" t="s">
         <v>672</v>
@@ -10332,7 +10327,7 @@
         <v>601</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G282" s="16" t="s">
         <v>793</v>
@@ -10356,7 +10351,7 @@
         <v>601</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G283" s="16" t="s">
         <v>683</v>
@@ -10380,7 +10375,7 @@
         <v>601</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G284" s="16" t="s">
         <v>743</v>
@@ -10404,7 +10399,7 @@
         <v>601</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G285" s="16" t="s">
         <v>850</v>
@@ -10428,7 +10423,7 @@
         <v>601</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G286" s="16" t="s">
         <v>642</v>
@@ -10452,7 +10447,7 @@
         <v>601</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G287" s="16" t="s">
         <v>717</v>
@@ -10476,7 +10471,7 @@
         <v>601</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G288" s="16" t="s">
         <v>871</v>
@@ -10500,7 +10495,7 @@
         <v>601</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G289" s="16" t="s">
         <v>855</v>
@@ -10524,7 +10519,7 @@
         <v>601</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G290" s="16" t="s">
         <v>840</v>
@@ -10548,7 +10543,7 @@
         <v>601</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G291" s="16" t="s">
         <v>680</v>
@@ -10572,7 +10567,7 @@
         <v>601</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G292" s="16" t="s">
         <v>678</v>
@@ -10596,7 +10591,7 @@
         <v>601</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G293" s="16" t="s">
         <v>741</v>
@@ -10620,7 +10615,7 @@
         <v>601</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G294" s="16" t="s">
         <v>758</v>
@@ -10644,7 +10639,7 @@
         <v>601</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G295" s="16" t="s">
         <v>725</v>
@@ -10654,63 +10649,63 @@
   </sheetData>
   <autoFilter ref="A1:G295" xr:uid="{9F38B8BA-4557-470F-96FC-6D7AF2400F22}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G138">
-      <sortCondition sortBy="cellColor" ref="D1:D295" dxfId="37"/>
+      <sortCondition sortBy="cellColor" ref="D1:D295" dxfId="36"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="36" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="275"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A295">
+    <cfRule type="duplicateValues" dxfId="34" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="566"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A295">
+    <cfRule type="duplicateValues" dxfId="27" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="35" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="320"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C295">
+    <cfRule type="duplicateValues" dxfId="22" priority="584"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="585"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="597"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C295">
+    <cfRule type="duplicateValues" dxfId="6" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C284:C295">
-    <cfRule type="duplicateValues" dxfId="34" priority="536"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:D1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:G1">
-    <cfRule type="duplicateValues" dxfId="32" priority="321"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A295">
-    <cfRule type="duplicateValues" dxfId="31" priority="560"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="561"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="562"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="563"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="564"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="565"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="566"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A295">
-    <cfRule type="duplicateValues" dxfId="24" priority="574"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="575"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="576"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="577"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C295">
-    <cfRule type="duplicateValues" dxfId="20" priority="582"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="583"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="584"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="585"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="586"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="587"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="588"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="589"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="590"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="591"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="592"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="593"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="594"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="595"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="596"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="597"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C295">
-    <cfRule type="duplicateValues" dxfId="4" priority="614"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="615"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="616"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="321"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
